--- a/processo_2/synthetic_proposals/PROPOSTA_026/ficha_pontuacao.xlsx
+++ b/processo_2/synthetic_proposals/PROPOSTA_026/ficha_pontuacao.xlsx
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr"/>
     </row>
@@ -680,17 +680,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr"/>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -726,17 +726,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -804,20 +804,28 @@
           <t>Revista Científica Avançada 1</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>6681-8683</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Revista Científica Avançada 2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2435-1771</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -916,13 +924,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G24" t="inlineStr"/>
     </row>
@@ -958,7 +966,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -981,7 +989,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1031,13 +1039,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G29" t="inlineStr"/>
     </row>
@@ -1050,17 +1058,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" t="inlineStr"/>
     </row>
@@ -1075,7 +1083,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
@@ -1118,7 +1126,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1141,7 +1149,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1187,7 +1195,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1210,7 +1218,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1233,7 +1241,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1256,7 +1264,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1279,7 +1287,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1302,17 +1310,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v>1.5</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G42" t="inlineStr"/>
     </row>
@@ -1325,17 +1333,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
         <v>1.5</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G43" t="inlineStr"/>
     </row>
@@ -1369,13 +1377,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G45" t="inlineStr"/>
     </row>
@@ -1461,13 +1469,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G49" t="inlineStr"/>
     </row>
@@ -1484,13 +1492,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G50" t="inlineStr"/>
     </row>
@@ -1543,17 +1551,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>5</v>
       </c>
       <c r="F53" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G53" t="inlineStr"/>
     </row>
@@ -1566,7 +1574,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1612,7 +1620,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1635,7 +1643,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1660,7 +1668,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
@@ -1776,13 +1784,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
         <v>4</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr"/>
     </row>
@@ -1843,7 +1851,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G67" t="inlineStr"/>
     </row>
@@ -1858,7 +1866,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G68" t="inlineStr"/>
     </row>
